--- a/artfynd/A 35485-2025 artfynd.xlsx
+++ b/artfynd/A 35485-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -794,6 +794,115 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>127613328</v>
+      </c>
+      <c r="B3" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Oxeråsen S om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>443545</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6767246</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35485-2025 artfynd.xlsx
+++ b/artfynd/A 35485-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -903,6 +903,3154 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>127723307</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>443521</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6767377</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>127723609</v>
+      </c>
+      <c r="B5" t="n">
+        <v>77996</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>443546</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6767277</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På naturlig högstubbe med fyra brandljud</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127723015</v>
+      </c>
+      <c r="B6" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>443662</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6767258</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127723012</v>
+      </c>
+      <c r="B7" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>443607</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6767249</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127723576</v>
+      </c>
+      <c r="B8" t="n">
+        <v>78685</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>353</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>443532</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6767258</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127723402</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>443667</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6767260</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127722866</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>443824</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6767217</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127723059</v>
+      </c>
+      <c r="B11" t="n">
+        <v>78776</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>443538</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6767298</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127723054</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80993</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>443535</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6767296</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127723556</v>
+      </c>
+      <c r="B13" t="n">
+        <v>92620</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>443515</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6767361</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127723309</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>443523</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6767394</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127723308</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>443530</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6767386</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127723014</v>
+      </c>
+      <c r="B16" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>443651</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6767277</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127729140</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92620</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Oxeråsen S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>443528</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6767247</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127723016</v>
+      </c>
+      <c r="B18" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>443673</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6767268</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127723068</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92652</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1968</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Grantaggsvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Phellodon violascens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>443537</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6767220</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Med grov gran i bäckmiljö</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127723017</v>
+      </c>
+      <c r="B20" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>443679</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6767256</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>127723306</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>443504</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6767355</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>127722979</v>
+      </c>
+      <c r="B22" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>443487</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6767358</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>127723019</v>
+      </c>
+      <c r="B23" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>443716</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6767260</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>127722984</v>
+      </c>
+      <c r="B24" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>443515</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6767222</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>127723401</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>443653</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6767260</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>127722982</v>
+      </c>
+      <c r="B26" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>443563</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6767324</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>127723018</v>
+      </c>
+      <c r="B27" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>443697</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6767275</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>127722824</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79636</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>443688</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6767261</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>127723013</v>
+      </c>
+      <c r="B29" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>443647</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6767284</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>127722980</v>
+      </c>
+      <c r="B30" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>443513</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6767360</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>127729074</v>
+      </c>
+      <c r="B31" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Oxeråsen S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>443523</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6767226</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>127729095</v>
+      </c>
+      <c r="B32" t="n">
+        <v>92652</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1968</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Grantaggsvamp</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Phellodon violascens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Oxeråsen S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>443537</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6767222</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>17:18</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>17:18</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>127722983</v>
+      </c>
+      <c r="B33" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>443544</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6767299</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>127722869</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57821</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>443535</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6767220</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35485-2025 artfynd.xlsx
+++ b/artfynd/A 35485-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>127613328</v>
       </c>
       <c r="B3" t="n">
-        <v>92632</v>
+        <v>92634</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>127723307</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>127723609</v>
       </c>
       <c r="B5" t="n">
-        <v>77996</v>
+        <v>77998</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,47 +1104,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127723015</v>
+        <v>127723576</v>
       </c>
       <c r="B6" t="n">
-        <v>8450</v>
+        <v>78687</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>443662</v>
+        <v>443532</v>
       </c>
       <c r="R6" t="n">
         <v>6767258</v>
@@ -1206,50 +1201,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127723012</v>
+        <v>127723402</v>
       </c>
       <c r="B7" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>443607</v>
+        <v>443667</v>
       </c>
       <c r="R7" t="n">
-        <v>6767249</v>
+        <v>6767260</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,10 +1298,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127723576</v>
+        <v>127722866</v>
       </c>
       <c r="B8" t="n">
-        <v>78685</v>
+        <v>57663</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1319,34 +1309,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>443532</v>
+        <v>443824</v>
       </c>
       <c r="R8" t="n">
-        <v>6767258</v>
+        <v>6767217</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1405,45 +1400,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127723402</v>
+        <v>127723015</v>
       </c>
       <c r="B9" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>443667</v>
+        <v>443662</v>
       </c>
       <c r="R9" t="n">
-        <v>6767260</v>
+        <v>6767258</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1502,38 +1502,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127722866</v>
+        <v>127723012</v>
       </c>
       <c r="B10" t="n">
-        <v>57661</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1542,10 +1542,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>443824</v>
+        <v>443607</v>
       </c>
       <c r="R10" t="n">
-        <v>6767217</v>
+        <v>6767249</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1607,7 +1607,7 @@
         <v>127723059</v>
       </c>
       <c r="B11" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>127723054</v>
       </c>
       <c r="B12" t="n">
-        <v>80993</v>
+        <v>80995</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>127723556</v>
       </c>
       <c r="B13" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>127723309</v>
       </c>
       <c r="B14" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>127723308</v>
       </c>
       <c r="B15" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2192,10 +2192,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127729140</v>
+        <v>127723016</v>
       </c>
       <c r="B17" t="n">
-        <v>92620</v>
+        <v>8450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2203,45 +2203,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>443528</v>
+        <v>443673</v>
       </c>
       <c r="R17" t="n">
-        <v>6767247</v>
+        <v>6767268</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2271,90 +2265,74 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>17:24</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>17:24</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127723016</v>
+        <v>127723068</v>
       </c>
       <c r="B18" t="n">
-        <v>8450</v>
+        <v>92654</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>1968</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>443673</v>
+        <v>443537</v>
       </c>
       <c r="R18" t="n">
-        <v>6767268</v>
+        <v>6767220</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2389,12 +2367,18 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Med grov gran i bäckmiljö</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2413,45 +2397,56 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127723068</v>
+        <v>127729140</v>
       </c>
       <c r="B19" t="n">
-        <v>92652</v>
+        <v>92622</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1968</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>443537</v>
+        <v>443528</v>
       </c>
       <c r="R19" t="n">
-        <v>6767220</v>
+        <v>6767247</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2481,14 +2476,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Med grov gran i bäckmiljö</t>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2504,12 +2504,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2621,7 +2621,7 @@
         <v>127723306</v>
       </c>
       <c r="B21" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2919,50 +2919,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127722984</v>
+        <v>127723401</v>
       </c>
       <c r="B24" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>443515</v>
+        <v>443653</v>
       </c>
       <c r="R24" t="n">
-        <v>6767222</v>
+        <v>6767260</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,45 +3016,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127723401</v>
+        <v>127722984</v>
       </c>
       <c r="B25" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>443653</v>
+        <v>443515</v>
       </c>
       <c r="R25" t="n">
-        <v>6767260</v>
+        <v>6767222</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3325,7 +3325,7 @@
         <v>127722824</v>
       </c>
       <c r="B28" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3521,10 +3521,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127722980</v>
+        <v>127729074</v>
       </c>
       <c r="B30" t="n">
-        <v>8450</v>
+        <v>92634</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3532,39 +3532,45 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>4366</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>443513</v>
+        <v>443523</v>
       </c>
       <c r="R30" t="n">
-        <v>6767360</v>
+        <v>6767226</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3594,39 +3600,50 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127729074</v>
+        <v>127722980</v>
       </c>
       <c r="B31" t="n">
-        <v>92632</v>
+        <v>8450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3634,45 +3651,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4366</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>443523</v>
+        <v>443513</v>
       </c>
       <c r="R31" t="n">
-        <v>6767226</v>
+        <v>6767360</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3702,40 +3713,29 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>17:22</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>17:22</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3745,7 +3745,7 @@
         <v>127729095</v>
       </c>
       <c r="B32" t="n">
-        <v>92652</v>
+        <v>92654</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>127722869</v>
       </c>
       <c r="B34" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 35485-2025 artfynd.xlsx
+++ b/artfynd/A 35485-2025 artfynd.xlsx
@@ -1702,45 +1702,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127723054</v>
+        <v>127723014</v>
       </c>
       <c r="B12" t="n">
-        <v>80995</v>
+        <v>8450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1049</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>443535</v>
+        <v>443651</v>
       </c>
       <c r="R12" t="n">
-        <v>6767296</v>
+        <v>6767277</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1799,32 +1804,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127723556</v>
+        <v>127723054</v>
       </c>
       <c r="B13" t="n">
-        <v>92622</v>
+        <v>80995</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>1049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1834,10 +1839,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>443515</v>
+        <v>443535</v>
       </c>
       <c r="R13" t="n">
-        <v>6767361</v>
+        <v>6767296</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1896,32 +1901,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127723309</v>
+        <v>127723556</v>
       </c>
       <c r="B14" t="n">
-        <v>79020</v>
+        <v>92622</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1931,10 +1936,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>443523</v>
+        <v>443515</v>
       </c>
       <c r="R14" t="n">
-        <v>6767394</v>
+        <v>6767361</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1993,7 +1998,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127723308</v>
+        <v>127723309</v>
       </c>
       <c r="B15" t="n">
         <v>79020</v>
@@ -2028,10 +2033,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>443530</v>
+        <v>443523</v>
       </c>
       <c r="R15" t="n">
-        <v>6767386</v>
+        <v>6767394</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2090,50 +2095,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127723014</v>
+        <v>127723308</v>
       </c>
       <c r="B16" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>443651</v>
+        <v>443530</v>
       </c>
       <c r="R16" t="n">
-        <v>6767277</v>
+        <v>6767386</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2192,50 +2192,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127723016</v>
+        <v>127723068</v>
       </c>
       <c r="B17" t="n">
-        <v>8450</v>
+        <v>92654</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>1968</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>443673</v>
+        <v>443537</v>
       </c>
       <c r="R17" t="n">
-        <v>6767268</v>
+        <v>6767220</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2270,12 +2265,18 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Med grov gran i bäckmiljö</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2294,45 +2295,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127723068</v>
+        <v>127723016</v>
       </c>
       <c r="B18" t="n">
-        <v>92654</v>
+        <v>8450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1968</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>443537</v>
+        <v>443673</v>
       </c>
       <c r="R18" t="n">
-        <v>6767220</v>
+        <v>6767268</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2367,18 +2373,12 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Med grov gran i bäckmiljö</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2919,45 +2919,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127723401</v>
+        <v>127722984</v>
       </c>
       <c r="B24" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>443653</v>
+        <v>443515</v>
       </c>
       <c r="R24" t="n">
-        <v>6767260</v>
+        <v>6767222</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3016,50 +3021,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127722984</v>
+        <v>127723401</v>
       </c>
       <c r="B25" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>443515</v>
+        <v>443653</v>
       </c>
       <c r="R25" t="n">
-        <v>6767222</v>
+        <v>6767260</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 35485-2025 artfynd.xlsx
+++ b/artfynd/A 35485-2025 artfynd.xlsx
@@ -1604,10 +1604,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127723059</v>
+        <v>127723309</v>
       </c>
       <c r="B11" t="n">
-        <v>78778</v>
+        <v>79020</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1615,21 +1615,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>443538</v>
+        <v>443523</v>
       </c>
       <c r="R11" t="n">
-        <v>6767298</v>
+        <v>6767394</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1683,7 +1683,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1702,50 +1701,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127723014</v>
+        <v>127723308</v>
       </c>
       <c r="B12" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>443651</v>
+        <v>443530</v>
       </c>
       <c r="R12" t="n">
-        <v>6767277</v>
+        <v>6767386</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1804,45 +1798,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127723054</v>
+        <v>127723014</v>
       </c>
       <c r="B13" t="n">
-        <v>80995</v>
+        <v>8450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1049</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>443535</v>
+        <v>443651</v>
       </c>
       <c r="R13" t="n">
-        <v>6767296</v>
+        <v>6767277</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1901,32 +1900,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127723556</v>
+        <v>127723054</v>
       </c>
       <c r="B14" t="n">
-        <v>92622</v>
+        <v>80995</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>1049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1936,10 +1935,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>443515</v>
+        <v>443535</v>
       </c>
       <c r="R14" t="n">
-        <v>6767361</v>
+        <v>6767296</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1998,32 +1997,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127723309</v>
+        <v>127723556</v>
       </c>
       <c r="B15" t="n">
-        <v>79020</v>
+        <v>92622</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2033,10 +2032,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>443523</v>
+        <v>443515</v>
       </c>
       <c r="R15" t="n">
-        <v>6767394</v>
+        <v>6767361</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2095,10 +2094,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127723308</v>
+        <v>127723059</v>
       </c>
       <c r="B16" t="n">
-        <v>79020</v>
+        <v>78778</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2106,21 +2105,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2130,10 +2129,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>443530</v>
+        <v>443538</v>
       </c>
       <c r="R16" t="n">
-        <v>6767386</v>
+        <v>6767298</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2174,6 +2173,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35485-2025 artfynd.xlsx
+++ b/artfynd/A 35485-2025 artfynd.xlsx
@@ -1604,10 +1604,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127723309</v>
+        <v>127723054</v>
       </c>
       <c r="B11" t="n">
-        <v>79020</v>
+        <v>80995</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1615,21 +1615,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>443523</v>
+        <v>443535</v>
       </c>
       <c r="R11" t="n">
-        <v>6767394</v>
+        <v>6767296</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1798,50 +1798,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127723014</v>
+        <v>127723059</v>
       </c>
       <c r="B13" t="n">
-        <v>8450</v>
+        <v>78778</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>443651</v>
+        <v>443538</v>
       </c>
       <c r="R13" t="n">
-        <v>6767277</v>
+        <v>6767298</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1882,6 +1877,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1900,45 +1896,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127723054</v>
+        <v>127723014</v>
       </c>
       <c r="B14" t="n">
-        <v>80995</v>
+        <v>8450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1049</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>443535</v>
+        <v>443651</v>
       </c>
       <c r="R14" t="n">
-        <v>6767296</v>
+        <v>6767277</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2094,10 +2095,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127723059</v>
+        <v>127723309</v>
       </c>
       <c r="B16" t="n">
-        <v>78778</v>
+        <v>79020</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2105,21 +2106,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2129,10 +2130,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>443538</v>
+        <v>443523</v>
       </c>
       <c r="R16" t="n">
-        <v>6767298</v>
+        <v>6767394</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2173,7 +2174,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2192,45 +2192,56 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127723068</v>
+        <v>127729140</v>
       </c>
       <c r="B17" t="n">
-        <v>92654</v>
+        <v>92622</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1968</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>443537</v>
+        <v>443528</v>
       </c>
       <c r="R17" t="n">
-        <v>6767220</v>
+        <v>6767247</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2260,14 +2271,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Med grov gran i bäckmiljö</t>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2283,62 +2299,57 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127723016</v>
+        <v>127723068</v>
       </c>
       <c r="B18" t="n">
-        <v>8450</v>
+        <v>92654</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>1968</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>443673</v>
+        <v>443537</v>
       </c>
       <c r="R18" t="n">
-        <v>6767268</v>
+        <v>6767220</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2373,12 +2384,18 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Med grov gran i bäckmiljö</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2397,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127729140</v>
+        <v>127723016</v>
       </c>
       <c r="B19" t="n">
-        <v>92622</v>
+        <v>8450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2408,45 +2425,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>443528</v>
+        <v>443673</v>
       </c>
       <c r="R19" t="n">
-        <v>6767247</v>
+        <v>6767268</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2476,40 +2487,29 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>17:24</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>17:24</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 35485-2025 artfynd.xlsx
+++ b/artfynd/A 35485-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>127613328</v>
       </c>
       <c r="B3" t="n">
-        <v>92634</v>
+        <v>92640</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1701,10 +1701,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127723308</v>
+        <v>127723059</v>
       </c>
       <c r="B12" t="n">
-        <v>79020</v>
+        <v>78778</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1712,21 +1712,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1736,10 +1736,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>443530</v>
+        <v>443538</v>
       </c>
       <c r="R12" t="n">
-        <v>6767386</v>
+        <v>6767298</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1780,6 +1780,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1798,45 +1799,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127723059</v>
+        <v>127723014</v>
       </c>
       <c r="B13" t="n">
-        <v>78778</v>
+        <v>8450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>443538</v>
+        <v>443651</v>
       </c>
       <c r="R13" t="n">
-        <v>6767298</v>
+        <v>6767277</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1877,7 +1883,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1896,50 +1901,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127723014</v>
+        <v>127723309</v>
       </c>
       <c r="B14" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>443651</v>
+        <v>443523</v>
       </c>
       <c r="R14" t="n">
-        <v>6767277</v>
+        <v>6767394</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1998,32 +1998,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127723556</v>
+        <v>127723308</v>
       </c>
       <c r="B15" t="n">
-        <v>92622</v>
+        <v>79020</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2033,10 +2033,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>443515</v>
+        <v>443530</v>
       </c>
       <c r="R15" t="n">
-        <v>6767361</v>
+        <v>6767386</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2095,32 +2095,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127723309</v>
+        <v>127723556</v>
       </c>
       <c r="B16" t="n">
-        <v>79020</v>
+        <v>92628</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2130,10 +2130,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>443523</v>
+        <v>443515</v>
       </c>
       <c r="R16" t="n">
-        <v>6767394</v>
+        <v>6767361</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2192,56 +2192,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127729140</v>
+        <v>127723068</v>
       </c>
       <c r="B17" t="n">
-        <v>92622</v>
+        <v>92660</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>1968</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>443528</v>
+        <v>443537</v>
       </c>
       <c r="R17" t="n">
-        <v>6767247</v>
+        <v>6767220</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2271,19 +2260,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>17:24</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>17:24</t>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Med grov gran i bäckmiljö</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2299,57 +2283,68 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127723068</v>
+        <v>127729140</v>
       </c>
       <c r="B18" t="n">
-        <v>92654</v>
+        <v>92628</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1968</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>443537</v>
+        <v>443528</v>
       </c>
       <c r="R18" t="n">
-        <v>6767220</v>
+        <v>6767247</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2379,14 +2374,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Med grov gran i bäckmiljö</t>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2402,12 +2402,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2919,50 +2919,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127722984</v>
+        <v>127723401</v>
       </c>
       <c r="B24" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>443515</v>
+        <v>443653</v>
       </c>
       <c r="R24" t="n">
-        <v>6767222</v>
+        <v>6767260</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,45 +3016,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127723401</v>
+        <v>127722984</v>
       </c>
       <c r="B25" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>443653</v>
+        <v>443515</v>
       </c>
       <c r="R25" t="n">
-        <v>6767260</v>
+        <v>6767222</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3524,7 +3524,7 @@
         <v>127729074</v>
       </c>
       <c r="B30" t="n">
-        <v>92634</v>
+        <v>92640</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>127729095</v>
       </c>
       <c r="B32" t="n">
-        <v>92654</v>
+        <v>92660</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 35485-2025 artfynd.xlsx
+++ b/artfynd/A 35485-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>127613328</v>
       </c>
       <c r="B3" t="n">
-        <v>92640</v>
+        <v>92643</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127723307</v>
+        <v>127723609</v>
       </c>
       <c r="B4" t="n">
-        <v>79020</v>
+        <v>78001</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -916,21 +916,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -940,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>443521</v>
+        <v>443546</v>
       </c>
       <c r="R4" t="n">
-        <v>6767377</v>
+        <v>6767277</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,6 +976,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På naturlig högstubbe med fyra brandljud</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127723609</v>
+        <v>127723307</v>
       </c>
       <c r="B5" t="n">
-        <v>77998</v>
+        <v>79023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1013,21 +1018,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1037,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>443546</v>
+        <v>443521</v>
       </c>
       <c r="R5" t="n">
-        <v>6767277</v>
+        <v>6767377</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,11 +1078,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På naturlig högstubbe med fyra brandljud</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127723576</v>
+        <v>127723402</v>
       </c>
       <c r="B6" t="n">
-        <v>78687</v>
+        <v>79023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>443532</v>
+        <v>443667</v>
       </c>
       <c r="R6" t="n">
-        <v>6767258</v>
+        <v>6767260</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,10 +1201,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127723402</v>
+        <v>127722866</v>
       </c>
       <c r="B7" t="n">
-        <v>79020</v>
+        <v>57666</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1212,34 +1212,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>443667</v>
+        <v>443824</v>
       </c>
       <c r="R7" t="n">
-        <v>6767260</v>
+        <v>6767217</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1298,10 +1303,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127722866</v>
+        <v>127723576</v>
       </c>
       <c r="B8" t="n">
-        <v>57663</v>
+        <v>78690</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1309,39 +1314,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>443824</v>
+        <v>443532</v>
       </c>
       <c r="R8" t="n">
-        <v>6767217</v>
+        <v>6767258</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1604,32 +1604,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127723054</v>
+        <v>127723556</v>
       </c>
       <c r="B11" t="n">
-        <v>80995</v>
+        <v>92631</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1049</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>443535</v>
+        <v>443515</v>
       </c>
       <c r="R11" t="n">
-        <v>6767296</v>
+        <v>6767361</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1701,10 +1701,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127723059</v>
+        <v>127723308</v>
       </c>
       <c r="B12" t="n">
-        <v>78778</v>
+        <v>79023</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1712,21 +1712,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1736,10 +1736,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>443538</v>
+        <v>443530</v>
       </c>
       <c r="R12" t="n">
-        <v>6767298</v>
+        <v>6767386</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1780,7 +1780,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1901,10 +1900,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127723309</v>
+        <v>127723054</v>
       </c>
       <c r="B14" t="n">
-        <v>79020</v>
+        <v>80998</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1912,21 +1911,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1936,10 +1935,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>443523</v>
+        <v>443535</v>
       </c>
       <c r="R14" t="n">
-        <v>6767394</v>
+        <v>6767296</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1998,10 +1997,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127723308</v>
+        <v>127723309</v>
       </c>
       <c r="B15" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2033,10 +2032,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>443530</v>
+        <v>443523</v>
       </c>
       <c r="R15" t="n">
-        <v>6767386</v>
+        <v>6767394</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2095,32 +2094,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127723556</v>
+        <v>127723059</v>
       </c>
       <c r="B16" t="n">
-        <v>92628</v>
+        <v>78781</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2130,10 +2129,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>443515</v>
+        <v>443538</v>
       </c>
       <c r="R16" t="n">
-        <v>6767361</v>
+        <v>6767298</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2174,6 +2173,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2195,7 +2195,7 @@
         <v>127723068</v>
       </c>
       <c r="B17" t="n">
-        <v>92660</v>
+        <v>92663</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>127729140</v>
       </c>
       <c r="B18" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>127723306</v>
       </c>
       <c r="B21" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>127723401</v>
       </c>
       <c r="B24" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>127722824</v>
       </c>
       <c r="B28" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>127729074</v>
       </c>
       <c r="B30" t="n">
-        <v>92640</v>
+        <v>92643</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>127729095</v>
       </c>
       <c r="B32" t="n">
-        <v>92660</v>
+        <v>92663</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>127722869</v>
       </c>
       <c r="B34" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 35485-2025 artfynd.xlsx
+++ b/artfynd/A 35485-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>127613328</v>
       </c>
       <c r="B3" t="n">
-        <v>92643</v>
+        <v>92651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127723609</v>
+        <v>127723307</v>
       </c>
       <c r="B4" t="n">
-        <v>78001</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -916,21 +916,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -940,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>443546</v>
+        <v>443521</v>
       </c>
       <c r="R4" t="n">
-        <v>6767277</v>
+        <v>6767377</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,11 +976,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På naturlig högstubbe med fyra brandljud</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127723307</v>
+        <v>127723609</v>
       </c>
       <c r="B5" t="n">
-        <v>79023</v>
+        <v>78007</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1018,21 +1013,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1042,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>443521</v>
+        <v>443546</v>
       </c>
       <c r="R5" t="n">
-        <v>6767377</v>
+        <v>6767277</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,6 +1073,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På naturlig högstubbe med fyra brandljud</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127723402</v>
+        <v>127723576</v>
       </c>
       <c r="B6" t="n">
-        <v>79023</v>
+        <v>78696</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>443667</v>
+        <v>443532</v>
       </c>
       <c r="R6" t="n">
-        <v>6767260</v>
+        <v>6767258</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,10 +1201,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127722866</v>
+        <v>127723402</v>
       </c>
       <c r="B7" t="n">
-        <v>57666</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1212,39 +1212,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>443824</v>
+        <v>443667</v>
       </c>
       <c r="R7" t="n">
-        <v>6767217</v>
+        <v>6767260</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1303,10 +1298,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127723576</v>
+        <v>127722866</v>
       </c>
       <c r="B8" t="n">
-        <v>78690</v>
+        <v>57672</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1314,34 +1309,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>443532</v>
+        <v>443824</v>
       </c>
       <c r="R8" t="n">
-        <v>6767258</v>
+        <v>6767217</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1607,7 +1607,7 @@
         <v>127723556</v>
       </c>
       <c r="B11" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1701,10 +1701,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127723308</v>
+        <v>127723054</v>
       </c>
       <c r="B12" t="n">
-        <v>79023</v>
+        <v>81004</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1712,21 +1712,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1736,10 +1736,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>443530</v>
+        <v>443535</v>
       </c>
       <c r="R12" t="n">
-        <v>6767386</v>
+        <v>6767296</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1798,50 +1798,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127723014</v>
+        <v>127723309</v>
       </c>
       <c r="B13" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>443651</v>
+        <v>443523</v>
       </c>
       <c r="R13" t="n">
-        <v>6767277</v>
+        <v>6767394</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1900,10 +1895,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127723054</v>
+        <v>127723059</v>
       </c>
       <c r="B14" t="n">
-        <v>80998</v>
+        <v>78787</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1911,21 +1906,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1049</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1935,10 +1930,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>443535</v>
+        <v>443538</v>
       </c>
       <c r="R14" t="n">
-        <v>6767296</v>
+        <v>6767298</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1979,6 +1974,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1997,45 +1993,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127723309</v>
+        <v>127723014</v>
       </c>
       <c r="B15" t="n">
-        <v>79023</v>
+        <v>8450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>443523</v>
+        <v>443651</v>
       </c>
       <c r="R15" t="n">
-        <v>6767394</v>
+        <v>6767277</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2094,10 +2095,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127723059</v>
+        <v>127723308</v>
       </c>
       <c r="B16" t="n">
-        <v>78781</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2105,21 +2106,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2129,10 +2130,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>443538</v>
+        <v>443530</v>
       </c>
       <c r="R16" t="n">
-        <v>6767298</v>
+        <v>6767386</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2173,7 +2174,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2195,7 +2195,7 @@
         <v>127723068</v>
       </c>
       <c r="B17" t="n">
-        <v>92663</v>
+        <v>92671</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>127729140</v>
       </c>
       <c r="B18" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>127723306</v>
       </c>
       <c r="B21" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>127723401</v>
       </c>
       <c r="B24" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>127722824</v>
       </c>
       <c r="B28" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>127729074</v>
       </c>
       <c r="B30" t="n">
-        <v>92643</v>
+        <v>92651</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>127729095</v>
       </c>
       <c r="B32" t="n">
-        <v>92663</v>
+        <v>92671</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>127722869</v>
       </c>
       <c r="B34" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 35485-2025 artfynd.xlsx
+++ b/artfynd/A 35485-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>127613328</v>
       </c>
       <c r="B3" t="n">
-        <v>92651</v>
+        <v>92652</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127723307</v>
+        <v>127723609</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>78007</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -916,21 +916,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -940,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>443521</v>
+        <v>443546</v>
       </c>
       <c r="R4" t="n">
-        <v>6767377</v>
+        <v>6767277</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,6 +976,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På naturlig högstubbe med fyra brandljud</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127723609</v>
+        <v>127723307</v>
       </c>
       <c r="B5" t="n">
-        <v>78007</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1013,21 +1018,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1037,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>443546</v>
+        <v>443521</v>
       </c>
       <c r="R5" t="n">
-        <v>6767277</v>
+        <v>6767377</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,11 +1078,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På naturlig högstubbe med fyra brandljud</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127723576</v>
+        <v>127723402</v>
       </c>
       <c r="B6" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>443532</v>
+        <v>443667</v>
       </c>
       <c r="R6" t="n">
-        <v>6767258</v>
+        <v>6767260</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,10 +1201,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127723402</v>
+        <v>127722866</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1212,34 +1212,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>443667</v>
+        <v>443824</v>
       </c>
       <c r="R7" t="n">
-        <v>6767260</v>
+        <v>6767217</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1298,38 +1303,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127722866</v>
+        <v>127723015</v>
       </c>
       <c r="B8" t="n">
-        <v>57672</v>
+        <v>8450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1338,10 +1343,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>443824</v>
+        <v>443662</v>
       </c>
       <c r="R8" t="n">
-        <v>6767217</v>
+        <v>6767258</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1400,7 +1405,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127723015</v>
+        <v>127723012</v>
       </c>
       <c r="B9" t="n">
         <v>8450</v>
@@ -1440,10 +1445,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>443662</v>
+        <v>443607</v>
       </c>
       <c r="R9" t="n">
-        <v>6767258</v>
+        <v>6767249</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1502,50 +1507,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127723012</v>
+        <v>127723576</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>78696</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>443607</v>
+        <v>443532</v>
       </c>
       <c r="R10" t="n">
-        <v>6767249</v>
+        <v>6767258</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1607,7 +1607,7 @@
         <v>127723556</v>
       </c>
       <c r="B11" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1701,10 +1701,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127723054</v>
+        <v>127723059</v>
       </c>
       <c r="B12" t="n">
-        <v>81004</v>
+        <v>78787</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1712,21 +1712,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1049</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1736,10 +1736,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>443535</v>
+        <v>443538</v>
       </c>
       <c r="R12" t="n">
-        <v>6767296</v>
+        <v>6767298</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1780,6 +1780,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1895,10 +1896,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127723059</v>
+        <v>127723054</v>
       </c>
       <c r="B14" t="n">
-        <v>78787</v>
+        <v>81004</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1906,21 +1907,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>1049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1930,10 +1931,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>443538</v>
+        <v>443535</v>
       </c>
       <c r="R14" t="n">
-        <v>6767298</v>
+        <v>6767296</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1974,7 +1975,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1993,50 +1993,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127723014</v>
+        <v>127723308</v>
       </c>
       <c r="B15" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>443651</v>
+        <v>443530</v>
       </c>
       <c r="R15" t="n">
-        <v>6767277</v>
+        <v>6767386</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2095,45 +2090,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127723308</v>
+        <v>127723014</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>443530</v>
+        <v>443651</v>
       </c>
       <c r="R16" t="n">
-        <v>6767386</v>
+        <v>6767277</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2192,45 +2192,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127723068</v>
+        <v>127723016</v>
       </c>
       <c r="B17" t="n">
-        <v>92671</v>
+        <v>8450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1968</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>443537</v>
+        <v>443673</v>
       </c>
       <c r="R17" t="n">
-        <v>6767220</v>
+        <v>6767268</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2265,18 +2270,12 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Med grov gran i bäckmiljö</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2298,7 +2297,7 @@
         <v>127729140</v>
       </c>
       <c r="B18" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2414,50 +2413,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127723016</v>
+        <v>127723068</v>
       </c>
       <c r="B19" t="n">
-        <v>8450</v>
+        <v>92672</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>1968</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>443673</v>
+        <v>443537</v>
       </c>
       <c r="R19" t="n">
-        <v>6767268</v>
+        <v>6767220</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2492,12 +2486,18 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Med grov gran i bäckmiljö</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3524,7 +3524,7 @@
         <v>127729074</v>
       </c>
       <c r="B30" t="n">
-        <v>92651</v>
+        <v>92652</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>127729095</v>
       </c>
       <c r="B32" t="n">
-        <v>92671</v>
+        <v>92672</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 35485-2025 artfynd.xlsx
+++ b/artfynd/A 35485-2025 artfynd.xlsx
@@ -1303,47 +1303,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127723015</v>
+        <v>127723576</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>78696</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>443662</v>
+        <v>443532</v>
       </c>
       <c r="R8" t="n">
         <v>6767258</v>
@@ -1405,7 +1400,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127723012</v>
+        <v>127723015</v>
       </c>
       <c r="B9" t="n">
         <v>8450</v>
@@ -1445,10 +1440,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>443607</v>
+        <v>443662</v>
       </c>
       <c r="R9" t="n">
-        <v>6767249</v>
+        <v>6767258</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1507,45 +1502,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127723576</v>
+        <v>127723012</v>
       </c>
       <c r="B10" t="n">
-        <v>78696</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>443532</v>
+        <v>443607</v>
       </c>
       <c r="R10" t="n">
-        <v>6767258</v>
+        <v>6767249</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1604,32 +1604,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127723556</v>
+        <v>127723054</v>
       </c>
       <c r="B11" t="n">
-        <v>92640</v>
+        <v>81004</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>1049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>443515</v>
+        <v>443535</v>
       </c>
       <c r="R11" t="n">
-        <v>6767361</v>
+        <v>6767296</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127723054</v>
+        <v>127723308</v>
       </c>
       <c r="B14" t="n">
-        <v>81004</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1907,21 +1907,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1931,10 +1931,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>443535</v>
+        <v>443530</v>
       </c>
       <c r="R14" t="n">
-        <v>6767296</v>
+        <v>6767386</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1993,32 +1993,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127723308</v>
+        <v>127723556</v>
       </c>
       <c r="B15" t="n">
-        <v>79029</v>
+        <v>92640</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2028,10 +2028,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>443530</v>
+        <v>443515</v>
       </c>
       <c r="R15" t="n">
-        <v>6767386</v>
+        <v>6767361</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2192,10 +2192,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127723016</v>
+        <v>127729140</v>
       </c>
       <c r="B17" t="n">
-        <v>8450</v>
+        <v>92640</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2203,39 +2203,45 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>443673</v>
+        <v>443528</v>
       </c>
       <c r="R17" t="n">
-        <v>6767268</v>
+        <v>6767247</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2265,39 +2271,50 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127729140</v>
+        <v>127723016</v>
       </c>
       <c r="B18" t="n">
-        <v>92640</v>
+        <v>8450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2305,45 +2322,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>443528</v>
+        <v>443673</v>
       </c>
       <c r="R18" t="n">
-        <v>6767247</v>
+        <v>6767268</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2373,40 +2384,29 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>17:24</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>17:24</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2919,45 +2919,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127723401</v>
+        <v>127722984</v>
       </c>
       <c r="B24" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>443653</v>
+        <v>443515</v>
       </c>
       <c r="R24" t="n">
-        <v>6767260</v>
+        <v>6767222</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3016,50 +3021,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127722984</v>
+        <v>127723401</v>
       </c>
       <c r="B25" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>443515</v>
+        <v>443653</v>
       </c>
       <c r="R25" t="n">
-        <v>6767222</v>
+        <v>6767260</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 35485-2025 artfynd.xlsx
+++ b/artfynd/A 35485-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>127613328</v>
       </c>
       <c r="B3" t="n">
-        <v>92652</v>
+        <v>92653</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127723609</v>
+        <v>127723307</v>
       </c>
       <c r="B4" t="n">
-        <v>78007</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -916,21 +916,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -940,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>443546</v>
+        <v>443521</v>
       </c>
       <c r="R4" t="n">
-        <v>6767277</v>
+        <v>6767377</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,11 +976,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På naturlig högstubbe med fyra brandljud</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127723307</v>
+        <v>127723609</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>78007</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1018,21 +1013,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1042,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>443521</v>
+        <v>443546</v>
       </c>
       <c r="R5" t="n">
-        <v>6767377</v>
+        <v>6767277</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,6 +1073,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På naturlig högstubbe med fyra brandljud</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,45 +1104,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127723402</v>
+        <v>127723015</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>443667</v>
+        <v>443662</v>
       </c>
       <c r="R6" t="n">
-        <v>6767260</v>
+        <v>6767258</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,38 +1206,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127722866</v>
+        <v>127723012</v>
       </c>
       <c r="B7" t="n">
-        <v>57672</v>
+        <v>8450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1241,10 +1246,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>443824</v>
+        <v>443607</v>
       </c>
       <c r="R7" t="n">
-        <v>6767217</v>
+        <v>6767249</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1303,10 +1308,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127723576</v>
+        <v>127722866</v>
       </c>
       <c r="B8" t="n">
-        <v>78696</v>
+        <v>57672</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1314,34 +1319,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>443532</v>
+        <v>443824</v>
       </c>
       <c r="R8" t="n">
-        <v>6767258</v>
+        <v>6767217</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1400,47 +1410,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127723015</v>
+        <v>127723576</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>78696</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>443662</v>
+        <v>443532</v>
       </c>
       <c r="R9" t="n">
         <v>6767258</v>
@@ -1502,50 +1507,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127723012</v>
+        <v>127723402</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>443607</v>
+        <v>443667</v>
       </c>
       <c r="R10" t="n">
-        <v>6767249</v>
+        <v>6767260</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1604,10 +1604,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127723054</v>
+        <v>127723059</v>
       </c>
       <c r="B11" t="n">
-        <v>81004</v>
+        <v>78787</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1615,21 +1615,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1049</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>443535</v>
+        <v>443538</v>
       </c>
       <c r="R11" t="n">
-        <v>6767296</v>
+        <v>6767298</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1683,6 +1683,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1701,10 +1702,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127723059</v>
+        <v>127723309</v>
       </c>
       <c r="B12" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1712,21 +1713,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1736,10 +1737,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>443538</v>
+        <v>443523</v>
       </c>
       <c r="R12" t="n">
-        <v>6767298</v>
+        <v>6767394</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1780,7 +1781,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1799,7 +1799,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127723309</v>
+        <v>127723308</v>
       </c>
       <c r="B13" t="n">
         <v>79029</v>
@@ -1834,10 +1834,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>443523</v>
+        <v>443530</v>
       </c>
       <c r="R13" t="n">
-        <v>6767394</v>
+        <v>6767386</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1896,32 +1896,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127723308</v>
+        <v>127723556</v>
       </c>
       <c r="B14" t="n">
-        <v>79029</v>
+        <v>92641</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1931,10 +1931,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>443530</v>
+        <v>443515</v>
       </c>
       <c r="R14" t="n">
-        <v>6767386</v>
+        <v>6767361</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1993,10 +1993,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127723556</v>
+        <v>127723014</v>
       </c>
       <c r="B15" t="n">
-        <v>92640</v>
+        <v>8450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2004,34 +2004,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>443515</v>
+        <v>443651</v>
       </c>
       <c r="R15" t="n">
-        <v>6767361</v>
+        <v>6767277</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2090,50 +2095,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127723014</v>
+        <v>127723054</v>
       </c>
       <c r="B16" t="n">
-        <v>8450</v>
+        <v>81004</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>1049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>443651</v>
+        <v>443535</v>
       </c>
       <c r="R16" t="n">
-        <v>6767277</v>
+        <v>6767296</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2192,56 +2192,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127729140</v>
+        <v>127723068</v>
       </c>
       <c r="B17" t="n">
-        <v>92640</v>
+        <v>92673</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>1968</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>443528</v>
+        <v>443537</v>
       </c>
       <c r="R17" t="n">
-        <v>6767247</v>
+        <v>6767220</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2271,19 +2260,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>17:24</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>17:24</t>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Med grov gran i bäckmiljö</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2299,22 +2283,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127723016</v>
+        <v>127729140</v>
       </c>
       <c r="B18" t="n">
-        <v>8450</v>
+        <v>92641</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2322,39 +2306,45 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>443673</v>
+        <v>443528</v>
       </c>
       <c r="R18" t="n">
-        <v>6767268</v>
+        <v>6767247</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2384,74 +2374,90 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127723068</v>
+        <v>127723016</v>
       </c>
       <c r="B19" t="n">
-        <v>92672</v>
+        <v>8450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1968</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>443537</v>
+        <v>443673</v>
       </c>
       <c r="R19" t="n">
-        <v>6767220</v>
+        <v>6767268</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2486,18 +2492,12 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Med grov gran i bäckmiljö</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2919,50 +2919,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127722984</v>
+        <v>127723401</v>
       </c>
       <c r="B24" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>443515</v>
+        <v>443653</v>
       </c>
       <c r="R24" t="n">
-        <v>6767222</v>
+        <v>6767260</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,45 +3016,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127723401</v>
+        <v>127722984</v>
       </c>
       <c r="B25" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>443653</v>
+        <v>443515</v>
       </c>
       <c r="R25" t="n">
-        <v>6767260</v>
+        <v>6767222</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3521,10 +3521,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127729074</v>
+        <v>127722980</v>
       </c>
       <c r="B30" t="n">
-        <v>92652</v>
+        <v>8450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3532,45 +3532,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4366</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>443523</v>
+        <v>443513</v>
       </c>
       <c r="R30" t="n">
-        <v>6767226</v>
+        <v>6767360</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3600,50 +3594,39 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>17:22</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>17:22</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127722980</v>
+        <v>127729074</v>
       </c>
       <c r="B31" t="n">
-        <v>8450</v>
+        <v>92653</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3651,39 +3634,45 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>4366</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>443513</v>
+        <v>443523</v>
       </c>
       <c r="R31" t="n">
-        <v>6767360</v>
+        <v>6767226</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3713,29 +3702,40 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3745,7 +3745,7 @@
         <v>127729095</v>
       </c>
       <c r="B32" t="n">
-        <v>92672</v>
+        <v>92673</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 35485-2025 artfynd.xlsx
+++ b/artfynd/A 35485-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>127613328</v>
       </c>
       <c r="B3" t="n">
-        <v>92653</v>
+        <v>92654</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127723307</v>
+        <v>127723609</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>78007</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -916,21 +916,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -940,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>443521</v>
+        <v>443546</v>
       </c>
       <c r="R4" t="n">
-        <v>6767377</v>
+        <v>6767277</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,6 +976,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På naturlig högstubbe med fyra brandljud</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127723609</v>
+        <v>127723307</v>
       </c>
       <c r="B5" t="n">
-        <v>78007</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1013,21 +1018,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1037,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>443546</v>
+        <v>443521</v>
       </c>
       <c r="R5" t="n">
-        <v>6767277</v>
+        <v>6767377</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,11 +1078,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På naturlig högstubbe med fyra brandljud</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,47 +1104,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127723015</v>
+        <v>127723576</v>
       </c>
       <c r="B6" t="n">
-        <v>8450</v>
+        <v>78696</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>443662</v>
+        <v>443532</v>
       </c>
       <c r="R6" t="n">
         <v>6767258</v>
@@ -1206,7 +1201,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127723012</v>
+        <v>127723015</v>
       </c>
       <c r="B7" t="n">
         <v>8450</v>
@@ -1246,10 +1241,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>443607</v>
+        <v>443662</v>
       </c>
       <c r="R7" t="n">
-        <v>6767249</v>
+        <v>6767258</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,38 +1303,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127722866</v>
+        <v>127723012</v>
       </c>
       <c r="B8" t="n">
-        <v>57672</v>
+        <v>8450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1348,10 +1343,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>443824</v>
+        <v>443607</v>
       </c>
       <c r="R8" t="n">
-        <v>6767217</v>
+        <v>6767249</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1410,10 +1405,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127723576</v>
+        <v>127723402</v>
       </c>
       <c r="B9" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1421,21 +1416,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1445,10 +1440,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>443532</v>
+        <v>443667</v>
       </c>
       <c r="R9" t="n">
-        <v>6767258</v>
+        <v>6767260</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1507,10 +1502,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127723402</v>
+        <v>127722866</v>
       </c>
       <c r="B10" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1518,34 +1513,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>443667</v>
+        <v>443824</v>
       </c>
       <c r="R10" t="n">
-        <v>6767260</v>
+        <v>6767217</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1604,10 +1604,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127723059</v>
+        <v>127723054</v>
       </c>
       <c r="B11" t="n">
-        <v>78787</v>
+        <v>81004</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1615,21 +1615,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>1049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>443538</v>
+        <v>443535</v>
       </c>
       <c r="R11" t="n">
-        <v>6767298</v>
+        <v>6767296</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1683,7 +1683,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1702,10 +1701,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127723309</v>
+        <v>127723059</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1713,21 +1712,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1737,10 +1736,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>443523</v>
+        <v>443538</v>
       </c>
       <c r="R12" t="n">
-        <v>6767394</v>
+        <v>6767298</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1781,6 +1780,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1799,7 +1799,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127723308</v>
+        <v>127723309</v>
       </c>
       <c r="B13" t="n">
         <v>79029</v>
@@ -1834,10 +1834,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>443530</v>
+        <v>443523</v>
       </c>
       <c r="R13" t="n">
-        <v>6767386</v>
+        <v>6767394</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,7 +1899,7 @@
         <v>127723556</v>
       </c>
       <c r="B14" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1993,50 +1993,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127723014</v>
+        <v>127723308</v>
       </c>
       <c r="B15" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>443651</v>
+        <v>443530</v>
       </c>
       <c r="R15" t="n">
-        <v>6767277</v>
+        <v>6767386</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2095,45 +2090,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127723054</v>
+        <v>127723014</v>
       </c>
       <c r="B16" t="n">
-        <v>81004</v>
+        <v>8450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1049</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>443535</v>
+        <v>443651</v>
       </c>
       <c r="R16" t="n">
-        <v>6767296</v>
+        <v>6767277</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2192,45 +2192,56 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127723068</v>
+        <v>127729140</v>
       </c>
       <c r="B17" t="n">
-        <v>92673</v>
+        <v>92642</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1968</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>443537</v>
+        <v>443528</v>
       </c>
       <c r="R17" t="n">
-        <v>6767220</v>
+        <v>6767247</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2260,14 +2271,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Med grov gran i bäckmiljö</t>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2283,68 +2299,57 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127729140</v>
+        <v>127723068</v>
       </c>
       <c r="B18" t="n">
-        <v>92641</v>
+        <v>92674</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>1968</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>443528</v>
+        <v>443537</v>
       </c>
       <c r="R18" t="n">
-        <v>6767247</v>
+        <v>6767220</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2374,19 +2379,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>17:24</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>17:24</t>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Med grov gran i bäckmiljö</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2402,12 +2402,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -3521,10 +3521,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127722980</v>
+        <v>127729074</v>
       </c>
       <c r="B30" t="n">
-        <v>8450</v>
+        <v>92654</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3532,39 +3532,45 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>4366</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>443513</v>
+        <v>443523</v>
       </c>
       <c r="R30" t="n">
-        <v>6767360</v>
+        <v>6767226</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3594,39 +3600,50 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127729074</v>
+        <v>127722980</v>
       </c>
       <c r="B31" t="n">
-        <v>92653</v>
+        <v>8450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3634,45 +3651,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4366</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>443523</v>
+        <v>443513</v>
       </c>
       <c r="R31" t="n">
-        <v>6767226</v>
+        <v>6767360</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3702,40 +3713,29 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>17:22</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>17:22</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3745,7 +3745,7 @@
         <v>127729095</v>
       </c>
       <c r="B32" t="n">
-        <v>92673</v>
+        <v>92674</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 35485-2025 artfynd.xlsx
+++ b/artfynd/A 35485-2025 artfynd.xlsx
@@ -1201,50 +1201,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127723015</v>
+        <v>127723402</v>
       </c>
       <c r="B7" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>443662</v>
+        <v>443667</v>
       </c>
       <c r="R7" t="n">
-        <v>6767258</v>
+        <v>6767260</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1303,38 +1298,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127723012</v>
+        <v>127722866</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>57672</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1343,10 +1338,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>443607</v>
+        <v>443824</v>
       </c>
       <c r="R8" t="n">
-        <v>6767249</v>
+        <v>6767217</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1405,45 +1400,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127723402</v>
+        <v>127723012</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>443667</v>
+        <v>443607</v>
       </c>
       <c r="R9" t="n">
-        <v>6767260</v>
+        <v>6767249</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1502,38 +1502,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127722866</v>
+        <v>127723015</v>
       </c>
       <c r="B10" t="n">
-        <v>57672</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1542,10 +1542,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>443824</v>
+        <v>443662</v>
       </c>
       <c r="R10" t="n">
-        <v>6767217</v>
+        <v>6767258</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1604,45 +1604,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127723054</v>
+        <v>127723014</v>
       </c>
       <c r="B11" t="n">
-        <v>81004</v>
+        <v>8450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1049</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>443535</v>
+        <v>443651</v>
       </c>
       <c r="R11" t="n">
-        <v>6767296</v>
+        <v>6767277</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1799,10 +1804,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127723309</v>
+        <v>127723054</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>81004</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1810,21 +1815,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1834,10 +1839,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>443523</v>
+        <v>443535</v>
       </c>
       <c r="R13" t="n">
-        <v>6767394</v>
+        <v>6767296</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1993,7 +1998,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127723308</v>
+        <v>127723309</v>
       </c>
       <c r="B15" t="n">
         <v>79029</v>
@@ -2028,10 +2033,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>443530</v>
+        <v>443523</v>
       </c>
       <c r="R15" t="n">
-        <v>6767386</v>
+        <v>6767394</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2090,50 +2095,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127723014</v>
+        <v>127723308</v>
       </c>
       <c r="B16" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>443651</v>
+        <v>443530</v>
       </c>
       <c r="R16" t="n">
-        <v>6767277</v>
+        <v>6767386</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2192,10 +2192,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127729140</v>
+        <v>127723016</v>
       </c>
       <c r="B17" t="n">
-        <v>92642</v>
+        <v>8450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2203,45 +2203,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>443528</v>
+        <v>443673</v>
       </c>
       <c r="R17" t="n">
-        <v>6767247</v>
+        <v>6767268</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2271,40 +2265,29 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>17:24</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>17:24</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2414,10 +2397,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127723016</v>
+        <v>127729140</v>
       </c>
       <c r="B19" t="n">
-        <v>8450</v>
+        <v>92642</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2425,39 +2408,45 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>443673</v>
+        <v>443528</v>
       </c>
       <c r="R19" t="n">
-        <v>6767268</v>
+        <v>6767247</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2487,29 +2476,40 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2919,45 +2919,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127723401</v>
+        <v>127722984</v>
       </c>
       <c r="B24" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>443653</v>
+        <v>443515</v>
       </c>
       <c r="R24" t="n">
-        <v>6767260</v>
+        <v>6767222</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3016,50 +3021,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127722984</v>
+        <v>127723401</v>
       </c>
       <c r="B25" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>443515</v>
+        <v>443653</v>
       </c>
       <c r="R25" t="n">
-        <v>6767222</v>
+        <v>6767260</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 35485-2025 artfynd.xlsx
+++ b/artfynd/A 35485-2025 artfynd.xlsx
@@ -1104,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127723576</v>
+        <v>127723402</v>
       </c>
       <c r="B6" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>443532</v>
+        <v>443667</v>
       </c>
       <c r="R6" t="n">
-        <v>6767258</v>
+        <v>6767260</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,10 +1201,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127723402</v>
+        <v>127723576</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1212,21 +1212,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1236,10 +1236,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>443667</v>
+        <v>443532</v>
       </c>
       <c r="R7" t="n">
-        <v>6767260</v>
+        <v>6767258</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1604,50 +1604,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127723014</v>
+        <v>127723054</v>
       </c>
       <c r="B11" t="n">
-        <v>8450</v>
+        <v>81004</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>1049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>443651</v>
+        <v>443535</v>
       </c>
       <c r="R11" t="n">
-        <v>6767277</v>
+        <v>6767296</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1706,32 +1701,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127723059</v>
+        <v>127723556</v>
       </c>
       <c r="B12" t="n">
-        <v>78787</v>
+        <v>92642</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1741,10 +1736,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>443538</v>
+        <v>443515</v>
       </c>
       <c r="R12" t="n">
-        <v>6767298</v>
+        <v>6767361</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1785,7 +1780,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1804,10 +1798,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127723054</v>
+        <v>127723309</v>
       </c>
       <c r="B13" t="n">
-        <v>81004</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1815,21 +1809,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1839,10 +1833,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>443535</v>
+        <v>443523</v>
       </c>
       <c r="R13" t="n">
-        <v>6767296</v>
+        <v>6767394</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1901,32 +1895,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127723556</v>
+        <v>127723308</v>
       </c>
       <c r="B14" t="n">
-        <v>92642</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1936,10 +1930,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>443515</v>
+        <v>443530</v>
       </c>
       <c r="R14" t="n">
-        <v>6767361</v>
+        <v>6767386</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1998,10 +1992,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127723309</v>
+        <v>127723059</v>
       </c>
       <c r="B15" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2009,21 +2003,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2033,10 +2027,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>443523</v>
+        <v>443538</v>
       </c>
       <c r="R15" t="n">
-        <v>6767394</v>
+        <v>6767298</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2077,6 +2071,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2095,45 +2090,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127723308</v>
+        <v>127723014</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>443530</v>
+        <v>443651</v>
       </c>
       <c r="R16" t="n">
-        <v>6767386</v>
+        <v>6767277</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -3521,10 +3521,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127729074</v>
+        <v>127722980</v>
       </c>
       <c r="B30" t="n">
-        <v>92654</v>
+        <v>8450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3532,45 +3532,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4366</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>443523</v>
+        <v>443513</v>
       </c>
       <c r="R30" t="n">
-        <v>6767226</v>
+        <v>6767360</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3600,50 +3594,39 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>17:22</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>17:22</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127722980</v>
+        <v>127729074</v>
       </c>
       <c r="B31" t="n">
-        <v>8450</v>
+        <v>92654</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3651,39 +3634,45 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>4366</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>443513</v>
+        <v>443523</v>
       </c>
       <c r="R31" t="n">
-        <v>6767360</v>
+        <v>6767226</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3713,29 +3702,40 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>

--- a/artfynd/A 35485-2025 artfynd.xlsx
+++ b/artfynd/A 35485-2025 artfynd.xlsx
@@ -1104,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127723402</v>
+        <v>127723576</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>443667</v>
+        <v>443532</v>
       </c>
       <c r="R6" t="n">
-        <v>6767260</v>
+        <v>6767258</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,10 +1201,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127723576</v>
+        <v>127723402</v>
       </c>
       <c r="B7" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1212,21 +1212,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1236,10 +1236,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>443532</v>
+        <v>443667</v>
       </c>
       <c r="R7" t="n">
-        <v>6767258</v>
+        <v>6767260</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1604,45 +1604,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127723054</v>
+        <v>127723014</v>
       </c>
       <c r="B11" t="n">
-        <v>81004</v>
+        <v>8450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1049</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>443535</v>
+        <v>443651</v>
       </c>
       <c r="R11" t="n">
-        <v>6767296</v>
+        <v>6767277</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1701,32 +1706,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127723556</v>
+        <v>127723059</v>
       </c>
       <c r="B12" t="n">
-        <v>92642</v>
+        <v>78787</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1736,10 +1741,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>443515</v>
+        <v>443538</v>
       </c>
       <c r="R12" t="n">
-        <v>6767361</v>
+        <v>6767298</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1780,6 +1785,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1798,10 +1804,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127723309</v>
+        <v>127723054</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>81004</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1809,21 +1815,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1833,10 +1839,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>443523</v>
+        <v>443535</v>
       </c>
       <c r="R13" t="n">
-        <v>6767394</v>
+        <v>6767296</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1895,32 +1901,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127723308</v>
+        <v>127723556</v>
       </c>
       <c r="B14" t="n">
-        <v>79029</v>
+        <v>92642</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1930,10 +1936,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>443530</v>
+        <v>443515</v>
       </c>
       <c r="R14" t="n">
-        <v>6767386</v>
+        <v>6767361</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1992,10 +1998,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127723059</v>
+        <v>127723309</v>
       </c>
       <c r="B15" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2003,21 +2009,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2027,10 +2033,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>443538</v>
+        <v>443523</v>
       </c>
       <c r="R15" t="n">
-        <v>6767298</v>
+        <v>6767394</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2071,7 +2077,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2090,50 +2095,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127723014</v>
+        <v>127723308</v>
       </c>
       <c r="B16" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>443651</v>
+        <v>443530</v>
       </c>
       <c r="R16" t="n">
-        <v>6767277</v>
+        <v>6767386</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2192,50 +2192,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127723016</v>
+        <v>127723068</v>
       </c>
       <c r="B17" t="n">
-        <v>8450</v>
+        <v>92674</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>1968</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>443673</v>
+        <v>443537</v>
       </c>
       <c r="R17" t="n">
-        <v>6767268</v>
+        <v>6767220</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2270,12 +2265,18 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Med grov gran i bäckmiljö</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2294,45 +2295,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127723068</v>
+        <v>127723016</v>
       </c>
       <c r="B18" t="n">
-        <v>92674</v>
+        <v>8450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1968</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>443537</v>
+        <v>443673</v>
       </c>
       <c r="R18" t="n">
-        <v>6767220</v>
+        <v>6767268</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2367,18 +2373,12 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Med grov gran i bäckmiljö</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35485-2025 artfynd.xlsx
+++ b/artfynd/A 35485-2025 artfynd.xlsx
@@ -1604,50 +1604,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127723014</v>
+        <v>127723054</v>
       </c>
       <c r="B11" t="n">
-        <v>8450</v>
+        <v>81004</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>1049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>443651</v>
+        <v>443535</v>
       </c>
       <c r="R11" t="n">
-        <v>6767277</v>
+        <v>6767296</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1706,32 +1701,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127723059</v>
+        <v>127723556</v>
       </c>
       <c r="B12" t="n">
-        <v>78787</v>
+        <v>92642</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1741,10 +1736,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>443538</v>
+        <v>443515</v>
       </c>
       <c r="R12" t="n">
-        <v>6767298</v>
+        <v>6767361</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1785,7 +1780,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1804,10 +1798,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127723054</v>
+        <v>127723309</v>
       </c>
       <c r="B13" t="n">
-        <v>81004</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1815,21 +1809,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1839,10 +1833,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>443535</v>
+        <v>443523</v>
       </c>
       <c r="R13" t="n">
-        <v>6767296</v>
+        <v>6767394</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1901,32 +1895,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127723556</v>
+        <v>127723308</v>
       </c>
       <c r="B14" t="n">
-        <v>92642</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1936,10 +1930,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>443515</v>
+        <v>443530</v>
       </c>
       <c r="R14" t="n">
-        <v>6767361</v>
+        <v>6767386</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1998,10 +1992,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127723309</v>
+        <v>127723059</v>
       </c>
       <c r="B15" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2009,21 +2003,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2033,10 +2027,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>443523</v>
+        <v>443538</v>
       </c>
       <c r="R15" t="n">
-        <v>6767394</v>
+        <v>6767298</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2077,6 +2071,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2095,45 +2090,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127723308</v>
+        <v>127723014</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>443530</v>
+        <v>443651</v>
       </c>
       <c r="R16" t="n">
-        <v>6767386</v>
+        <v>6767277</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2192,45 +2192,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127723068</v>
+        <v>127723016</v>
       </c>
       <c r="B17" t="n">
-        <v>92674</v>
+        <v>8450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1968</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>443537</v>
+        <v>443673</v>
       </c>
       <c r="R17" t="n">
-        <v>6767220</v>
+        <v>6767268</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2265,18 +2270,12 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Med grov gran i bäckmiljö</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2295,50 +2294,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127723016</v>
+        <v>127723068</v>
       </c>
       <c r="B18" t="n">
-        <v>8450</v>
+        <v>92674</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>1968</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>443673</v>
+        <v>443537</v>
       </c>
       <c r="R18" t="n">
-        <v>6767268</v>
+        <v>6767220</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2373,12 +2367,18 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Med grov gran i bäckmiljö</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -3521,10 +3521,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127722980</v>
+        <v>127729074</v>
       </c>
       <c r="B30" t="n">
-        <v>8450</v>
+        <v>92654</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3532,39 +3532,45 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>4366</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>443513</v>
+        <v>443523</v>
       </c>
       <c r="R30" t="n">
-        <v>6767360</v>
+        <v>6767226</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3594,39 +3600,50 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127729074</v>
+        <v>127722980</v>
       </c>
       <c r="B31" t="n">
-        <v>92654</v>
+        <v>8450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3634,45 +3651,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4366</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>443523</v>
+        <v>443513</v>
       </c>
       <c r="R31" t="n">
-        <v>6767226</v>
+        <v>6767360</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3702,40 +3713,29 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>17:22</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>17:22</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>

--- a/artfynd/A 35485-2025 artfynd.xlsx
+++ b/artfynd/A 35485-2025 artfynd.xlsx
@@ -1201,10 +1201,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127723402</v>
+        <v>127722866</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1212,34 +1212,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>443667</v>
+        <v>443824</v>
       </c>
       <c r="R7" t="n">
-        <v>6767260</v>
+        <v>6767217</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1298,10 +1303,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127722866</v>
+        <v>127723402</v>
       </c>
       <c r="B8" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1309,39 +1314,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>443824</v>
+        <v>443667</v>
       </c>
       <c r="R8" t="n">
-        <v>6767217</v>
+        <v>6767260</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1604,45 +1604,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127723054</v>
+        <v>127723014</v>
       </c>
       <c r="B11" t="n">
-        <v>81004</v>
+        <v>8450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1049</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>443535</v>
+        <v>443651</v>
       </c>
       <c r="R11" t="n">
-        <v>6767296</v>
+        <v>6767277</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1701,32 +1706,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127723556</v>
+        <v>127723059</v>
       </c>
       <c r="B12" t="n">
-        <v>92642</v>
+        <v>78787</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1736,10 +1741,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>443515</v>
+        <v>443538</v>
       </c>
       <c r="R12" t="n">
-        <v>6767361</v>
+        <v>6767298</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1780,6 +1785,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1798,10 +1804,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127723309</v>
+        <v>127723054</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>81004</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1809,21 +1815,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1833,10 +1839,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>443523</v>
+        <v>443535</v>
       </c>
       <c r="R13" t="n">
-        <v>6767394</v>
+        <v>6767296</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1895,32 +1901,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127723308</v>
+        <v>127723556</v>
       </c>
       <c r="B14" t="n">
-        <v>79029</v>
+        <v>92642</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1930,10 +1936,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>443530</v>
+        <v>443515</v>
       </c>
       <c r="R14" t="n">
-        <v>6767386</v>
+        <v>6767361</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1992,10 +1998,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127723059</v>
+        <v>127723309</v>
       </c>
       <c r="B15" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2003,21 +2009,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2027,10 +2033,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>443538</v>
+        <v>443523</v>
       </c>
       <c r="R15" t="n">
-        <v>6767298</v>
+        <v>6767394</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2071,7 +2077,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2090,50 +2095,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127723014</v>
+        <v>127723308</v>
       </c>
       <c r="B16" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>443651</v>
+        <v>443530</v>
       </c>
       <c r="R16" t="n">
-        <v>6767277</v>
+        <v>6767386</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2192,50 +2192,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127723016</v>
+        <v>127723068</v>
       </c>
       <c r="B17" t="n">
-        <v>8450</v>
+        <v>92674</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>1968</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>443673</v>
+        <v>443537</v>
       </c>
       <c r="R17" t="n">
-        <v>6767268</v>
+        <v>6767220</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2270,12 +2265,18 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Med grov gran i bäckmiljö</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2294,45 +2295,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127723068</v>
+        <v>127723016</v>
       </c>
       <c r="B18" t="n">
-        <v>92674</v>
+        <v>8450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1968</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>443537</v>
+        <v>443673</v>
       </c>
       <c r="R18" t="n">
-        <v>6767220</v>
+        <v>6767268</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2367,18 +2373,12 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Med grov gran i bäckmiljö</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -3118,7 +3118,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127722982</v>
+        <v>127723018</v>
       </c>
       <c r="B26" t="n">
         <v>8450</v>
@@ -3158,10 +3158,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>443563</v>
+        <v>443697</v>
       </c>
       <c r="R26" t="n">
-        <v>6767324</v>
+        <v>6767275</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3220,7 +3220,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127723018</v>
+        <v>127722982</v>
       </c>
       <c r="B27" t="n">
         <v>8450</v>
@@ -3260,10 +3260,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>443697</v>
+        <v>443563</v>
       </c>
       <c r="R27" t="n">
-        <v>6767275</v>
+        <v>6767324</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3521,10 +3521,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127729074</v>
+        <v>127722980</v>
       </c>
       <c r="B30" t="n">
-        <v>92654</v>
+        <v>8450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3532,45 +3532,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4366</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>443523</v>
+        <v>443513</v>
       </c>
       <c r="R30" t="n">
-        <v>6767226</v>
+        <v>6767360</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3600,50 +3594,39 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>17:22</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>17:22</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127722980</v>
+        <v>127729074</v>
       </c>
       <c r="B31" t="n">
-        <v>8450</v>
+        <v>92654</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3651,39 +3634,45 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>4366</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>443513</v>
+        <v>443523</v>
       </c>
       <c r="R31" t="n">
-        <v>6767360</v>
+        <v>6767226</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3713,29 +3702,40 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>

--- a/artfynd/A 35485-2025 artfynd.xlsx
+++ b/artfynd/A 35485-2025 artfynd.xlsx
@@ -1201,10 +1201,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127722866</v>
+        <v>127723402</v>
       </c>
       <c r="B7" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1212,39 +1212,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>443824</v>
+        <v>443667</v>
       </c>
       <c r="R7" t="n">
-        <v>6767217</v>
+        <v>6767260</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1303,10 +1298,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127723402</v>
+        <v>127722866</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1314,34 +1309,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>443667</v>
+        <v>443824</v>
       </c>
       <c r="R8" t="n">
-        <v>6767260</v>
+        <v>6767217</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -3118,7 +3118,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127723018</v>
+        <v>127722982</v>
       </c>
       <c r="B26" t="n">
         <v>8450</v>
@@ -3158,10 +3158,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>443697</v>
+        <v>443563</v>
       </c>
       <c r="R26" t="n">
-        <v>6767275</v>
+        <v>6767324</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3220,7 +3220,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127722982</v>
+        <v>127723018</v>
       </c>
       <c r="B27" t="n">
         <v>8450</v>
@@ -3260,10 +3260,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>443563</v>
+        <v>443697</v>
       </c>
       <c r="R27" t="n">
-        <v>6767324</v>
+        <v>6767275</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 35485-2025 artfynd.xlsx
+++ b/artfynd/A 35485-2025 artfynd.xlsx
@@ -1201,10 +1201,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127723402</v>
+        <v>127722866</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1212,34 +1212,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>443667</v>
+        <v>443824</v>
       </c>
       <c r="R7" t="n">
-        <v>6767260</v>
+        <v>6767217</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1298,10 +1303,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127722866</v>
+        <v>127723402</v>
       </c>
       <c r="B8" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1309,39 +1314,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>443824</v>
+        <v>443667</v>
       </c>
       <c r="R8" t="n">
-        <v>6767217</v>
+        <v>6767260</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1604,50 +1604,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127723014</v>
+        <v>127723054</v>
       </c>
       <c r="B11" t="n">
-        <v>8450</v>
+        <v>81004</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>1049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>443651</v>
+        <v>443535</v>
       </c>
       <c r="R11" t="n">
-        <v>6767277</v>
+        <v>6767296</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1706,32 +1701,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127723059</v>
+        <v>127723556</v>
       </c>
       <c r="B12" t="n">
-        <v>78787</v>
+        <v>92642</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1741,10 +1736,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>443538</v>
+        <v>443515</v>
       </c>
       <c r="R12" t="n">
-        <v>6767298</v>
+        <v>6767361</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1785,7 +1780,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1804,10 +1798,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127723054</v>
+        <v>127723309</v>
       </c>
       <c r="B13" t="n">
-        <v>81004</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1815,21 +1809,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1839,10 +1833,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>443535</v>
+        <v>443523</v>
       </c>
       <c r="R13" t="n">
-        <v>6767296</v>
+        <v>6767394</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1901,32 +1895,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127723556</v>
+        <v>127723308</v>
       </c>
       <c r="B14" t="n">
-        <v>92642</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1936,10 +1930,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>443515</v>
+        <v>443530</v>
       </c>
       <c r="R14" t="n">
-        <v>6767361</v>
+        <v>6767386</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1998,10 +1992,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127723309</v>
+        <v>127723059</v>
       </c>
       <c r="B15" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2009,21 +2003,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2033,10 +2027,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>443523</v>
+        <v>443538</v>
       </c>
       <c r="R15" t="n">
-        <v>6767394</v>
+        <v>6767298</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2077,6 +2071,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2095,45 +2090,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127723308</v>
+        <v>127723014</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>443530</v>
+        <v>443651</v>
       </c>
       <c r="R16" t="n">
-        <v>6767386</v>
+        <v>6767277</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2192,45 +2192,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127723068</v>
+        <v>127723016</v>
       </c>
       <c r="B17" t="n">
-        <v>92674</v>
+        <v>8450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1968</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>443537</v>
+        <v>443673</v>
       </c>
       <c r="R17" t="n">
-        <v>6767220</v>
+        <v>6767268</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2265,18 +2270,12 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Med grov gran i bäckmiljö</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2295,50 +2294,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127723016</v>
+        <v>127723068</v>
       </c>
       <c r="B18" t="n">
-        <v>8450</v>
+        <v>92674</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>1968</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>443673</v>
+        <v>443537</v>
       </c>
       <c r="R18" t="n">
-        <v>6767268</v>
+        <v>6767220</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2373,12 +2367,18 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Med grov gran i bäckmiljö</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -3118,7 +3118,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127722982</v>
+        <v>127723018</v>
       </c>
       <c r="B26" t="n">
         <v>8450</v>
@@ -3158,10 +3158,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>443563</v>
+        <v>443697</v>
       </c>
       <c r="R26" t="n">
-        <v>6767324</v>
+        <v>6767275</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3220,7 +3220,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127723018</v>
+        <v>127722982</v>
       </c>
       <c r="B27" t="n">
         <v>8450</v>
@@ -3260,10 +3260,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>443697</v>
+        <v>443563</v>
       </c>
       <c r="R27" t="n">
-        <v>6767275</v>
+        <v>6767324</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3521,10 +3521,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127722980</v>
+        <v>127729074</v>
       </c>
       <c r="B30" t="n">
-        <v>8450</v>
+        <v>92654</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3532,39 +3532,45 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>4366</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>443513</v>
+        <v>443523</v>
       </c>
       <c r="R30" t="n">
-        <v>6767360</v>
+        <v>6767226</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3594,39 +3600,50 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127729074</v>
+        <v>127722980</v>
       </c>
       <c r="B31" t="n">
-        <v>92654</v>
+        <v>8450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3634,45 +3651,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4366</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>443523</v>
+        <v>443513</v>
       </c>
       <c r="R31" t="n">
-        <v>6767226</v>
+        <v>6767360</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3702,40 +3713,29 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>17:22</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>17:22</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>

--- a/artfynd/A 35485-2025 artfynd.xlsx
+++ b/artfynd/A 35485-2025 artfynd.xlsx
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127723609</v>
+        <v>127723307</v>
       </c>
       <c r="B4" t="n">
-        <v>78007</v>
+        <v>79032</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -916,21 +916,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -940,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>443546</v>
+        <v>443521</v>
       </c>
       <c r="R4" t="n">
-        <v>6767277</v>
+        <v>6767377</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,11 +976,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På naturlig högstubbe med fyra brandljud</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127723307</v>
+        <v>127723609</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>78010</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1018,21 +1013,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1042,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>443521</v>
+        <v>443546</v>
       </c>
       <c r="R5" t="n">
-        <v>6767377</v>
+        <v>6767277</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,6 +1073,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På naturlig högstubbe med fyra brandljud</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127723576</v>
+        <v>127722866</v>
       </c>
       <c r="B6" t="n">
-        <v>78696</v>
+        <v>57673</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1115,34 +1115,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>443532</v>
+        <v>443824</v>
       </c>
       <c r="R6" t="n">
-        <v>6767258</v>
+        <v>6767217</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127722866</v>
+        <v>127723576</v>
       </c>
       <c r="B7" t="n">
-        <v>57672</v>
+        <v>78699</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1212,39 +1217,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>443824</v>
+        <v>443532</v>
       </c>
       <c r="R7" t="n">
-        <v>6767217</v>
+        <v>6767258</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1306,7 +1306,7 @@
         <v>127723402</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127723012</v>
+        <v>127723015</v>
       </c>
       <c r="B9" t="n">
         <v>8450</v>
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>443607</v>
+        <v>443662</v>
       </c>
       <c r="R9" t="n">
-        <v>6767249</v>
+        <v>6767258</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1502,7 +1502,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127723015</v>
+        <v>127723012</v>
       </c>
       <c r="B10" t="n">
         <v>8450</v>
@@ -1542,10 +1542,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>443662</v>
+        <v>443607</v>
       </c>
       <c r="R10" t="n">
-        <v>6767258</v>
+        <v>6767249</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1604,45 +1604,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127723054</v>
+        <v>127723014</v>
       </c>
       <c r="B11" t="n">
-        <v>81004</v>
+        <v>8450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1049</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>443535</v>
+        <v>443651</v>
       </c>
       <c r="R11" t="n">
-        <v>6767296</v>
+        <v>6767277</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1701,32 +1706,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127723556</v>
+        <v>127723308</v>
       </c>
       <c r="B12" t="n">
-        <v>92642</v>
+        <v>79032</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1736,10 +1741,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>443515</v>
+        <v>443530</v>
       </c>
       <c r="R12" t="n">
-        <v>6767361</v>
+        <v>6767386</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1798,10 +1803,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127723309</v>
+        <v>127723054</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>81007</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1809,21 +1814,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1833,10 +1838,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>443523</v>
+        <v>443535</v>
       </c>
       <c r="R13" t="n">
-        <v>6767394</v>
+        <v>6767296</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1895,10 +1900,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127723308</v>
+        <v>127723059</v>
       </c>
       <c r="B14" t="n">
-        <v>79029</v>
+        <v>78790</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1906,21 +1911,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1930,10 +1935,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>443530</v>
+        <v>443538</v>
       </c>
       <c r="R14" t="n">
-        <v>6767386</v>
+        <v>6767298</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1974,6 +1979,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1992,10 +1998,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127723059</v>
+        <v>127723309</v>
       </c>
       <c r="B15" t="n">
-        <v>78787</v>
+        <v>79032</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2003,21 +2009,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2027,10 +2033,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>443538</v>
+        <v>443523</v>
       </c>
       <c r="R15" t="n">
-        <v>6767298</v>
+        <v>6767394</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2071,7 +2077,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2090,10 +2095,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127723014</v>
+        <v>127723556</v>
       </c>
       <c r="B16" t="n">
-        <v>8450</v>
+        <v>92650</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2101,39 +2106,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>443651</v>
+        <v>443515</v>
       </c>
       <c r="R16" t="n">
-        <v>6767277</v>
+        <v>6767361</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2297,7 +2297,7 @@
         <v>127723068</v>
       </c>
       <c r="B18" t="n">
-        <v>92674</v>
+        <v>92682</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         <v>127729140</v>
       </c>
       <c r="B19" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>127723306</v>
       </c>
       <c r="B21" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>127723401</v>
       </c>
       <c r="B25" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127723018</v>
+        <v>127722982</v>
       </c>
       <c r="B26" t="n">
         <v>8450</v>
@@ -3158,10 +3158,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>443697</v>
+        <v>443563</v>
       </c>
       <c r="R26" t="n">
-        <v>6767275</v>
+        <v>6767324</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3220,7 +3220,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127722982</v>
+        <v>127723018</v>
       </c>
       <c r="B27" t="n">
         <v>8450</v>
@@ -3260,10 +3260,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>443563</v>
+        <v>443697</v>
       </c>
       <c r="R27" t="n">
-        <v>6767324</v>
+        <v>6767275</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3325,7 +3325,7 @@
         <v>127722824</v>
       </c>
       <c r="B28" t="n">
-        <v>79647</v>
+        <v>79650</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>127729074</v>
       </c>
       <c r="B30" t="n">
-        <v>92654</v>
+        <v>92662</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>127729095</v>
       </c>
       <c r="B32" t="n">
-        <v>92674</v>
+        <v>92682</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>127722869</v>
       </c>
       <c r="B34" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 35485-2025 artfynd.xlsx
+++ b/artfynd/A 35485-2025 artfynd.xlsx
@@ -1104,38 +1104,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127722866</v>
+        <v>127723015</v>
       </c>
       <c r="B6" t="n">
-        <v>57673</v>
+        <v>8450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1144,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>443824</v>
+        <v>443662</v>
       </c>
       <c r="R6" t="n">
-        <v>6767217</v>
+        <v>6767258</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,45 +1206,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127723576</v>
+        <v>127723012</v>
       </c>
       <c r="B7" t="n">
-        <v>78699</v>
+        <v>8450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>443532</v>
+        <v>443607</v>
       </c>
       <c r="R7" t="n">
-        <v>6767258</v>
+        <v>6767249</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1303,10 +1308,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127723402</v>
+        <v>127723576</v>
       </c>
       <c r="B8" t="n">
-        <v>79032</v>
+        <v>78699</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1314,21 +1319,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1338,10 +1343,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>443667</v>
+        <v>443532</v>
       </c>
       <c r="R8" t="n">
-        <v>6767260</v>
+        <v>6767258</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1400,38 +1405,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127723015</v>
+        <v>127722866</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>57673</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1440,10 +1445,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>443662</v>
+        <v>443824</v>
       </c>
       <c r="R9" t="n">
-        <v>6767258</v>
+        <v>6767217</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1502,50 +1507,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127723012</v>
+        <v>127723402</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>79032</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>443607</v>
+        <v>443667</v>
       </c>
       <c r="R10" t="n">
-        <v>6767249</v>
+        <v>6767260</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -2294,45 +2294,56 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127723068</v>
+        <v>127729140</v>
       </c>
       <c r="B18" t="n">
-        <v>92682</v>
+        <v>92650</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1968</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>443537</v>
+        <v>443528</v>
       </c>
       <c r="R18" t="n">
-        <v>6767220</v>
+        <v>6767247</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2362,14 +2373,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Med grov gran i bäckmiljö</t>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2385,68 +2401,57 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127729140</v>
+        <v>127723068</v>
       </c>
       <c r="B19" t="n">
-        <v>92650</v>
+        <v>92682</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>1968</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>443528</v>
+        <v>443537</v>
       </c>
       <c r="R19" t="n">
-        <v>6767247</v>
+        <v>6767220</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2476,19 +2481,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>17:24</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>17:24</t>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Med grov gran i bäckmiljö</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2504,12 +2504,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -3521,10 +3521,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127729074</v>
+        <v>127722980</v>
       </c>
       <c r="B30" t="n">
-        <v>92662</v>
+        <v>8450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3532,45 +3532,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4366</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>443523</v>
+        <v>443513</v>
       </c>
       <c r="R30" t="n">
-        <v>6767226</v>
+        <v>6767360</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3600,50 +3594,39 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>17:22</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>17:22</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127722980</v>
+        <v>127729074</v>
       </c>
       <c r="B31" t="n">
-        <v>8450</v>
+        <v>92662</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3651,39 +3634,45 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>4366</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>443513</v>
+        <v>443523</v>
       </c>
       <c r="R31" t="n">
-        <v>6767360</v>
+        <v>6767226</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3713,29 +3702,40 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>

--- a/artfynd/A 35485-2025 artfynd.xlsx
+++ b/artfynd/A 35485-2025 artfynd.xlsx
@@ -908,7 +908,7 @@
         <v>127723307</v>
       </c>
       <c r="B4" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>127723609</v>
       </c>
       <c r="B5" t="n">
-        <v>78010</v>
+        <v>78021</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,47 +1104,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127723015</v>
+        <v>127723576</v>
       </c>
       <c r="B6" t="n">
-        <v>8450</v>
+        <v>78710</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>443662</v>
+        <v>443532</v>
       </c>
       <c r="R6" t="n">
         <v>6767258</v>
@@ -1206,50 +1201,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127723012</v>
+        <v>127723402</v>
       </c>
       <c r="B7" t="n">
-        <v>8450</v>
+        <v>79043</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>443607</v>
+        <v>443667</v>
       </c>
       <c r="R7" t="n">
-        <v>6767249</v>
+        <v>6767260</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,10 +1298,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127723576</v>
+        <v>127722866</v>
       </c>
       <c r="B8" t="n">
-        <v>78699</v>
+        <v>57684</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1319,34 +1309,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>443532</v>
+        <v>443824</v>
       </c>
       <c r="R8" t="n">
-        <v>6767258</v>
+        <v>6767217</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1405,38 +1400,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127722866</v>
+        <v>127723015</v>
       </c>
       <c r="B9" t="n">
-        <v>57673</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1445,10 +1440,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>443824</v>
+        <v>443662</v>
       </c>
       <c r="R9" t="n">
-        <v>6767217</v>
+        <v>6767258</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1507,45 +1502,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127723402</v>
+        <v>127723012</v>
       </c>
       <c r="B10" t="n">
-        <v>79032</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>443667</v>
+        <v>443607</v>
       </c>
       <c r="R10" t="n">
-        <v>6767260</v>
+        <v>6767249</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1604,50 +1604,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127723014</v>
+        <v>127723309</v>
       </c>
       <c r="B11" t="n">
-        <v>8450</v>
+        <v>79043</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>443651</v>
+        <v>443523</v>
       </c>
       <c r="R11" t="n">
-        <v>6767277</v>
+        <v>6767394</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,7 +1704,7 @@
         <v>127723308</v>
       </c>
       <c r="B12" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1803,32 +1798,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127723054</v>
+        <v>127723556</v>
       </c>
       <c r="B13" t="n">
-        <v>81007</v>
+        <v>92661</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1049</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1838,10 +1833,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>443535</v>
+        <v>443515</v>
       </c>
       <c r="R13" t="n">
-        <v>6767296</v>
+        <v>6767361</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1900,45 +1895,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127723059</v>
+        <v>127723014</v>
       </c>
       <c r="B14" t="n">
-        <v>78790</v>
+        <v>8450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>443538</v>
+        <v>443651</v>
       </c>
       <c r="R14" t="n">
-        <v>6767298</v>
+        <v>6767277</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1979,7 +1979,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1998,10 +1997,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127723309</v>
+        <v>127723054</v>
       </c>
       <c r="B15" t="n">
-        <v>79032</v>
+        <v>81018</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2009,21 +2008,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2033,10 +2032,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>443523</v>
+        <v>443535</v>
       </c>
       <c r="R15" t="n">
-        <v>6767394</v>
+        <v>6767296</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2095,32 +2094,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127723556</v>
+        <v>127723059</v>
       </c>
       <c r="B16" t="n">
-        <v>92650</v>
+        <v>78801</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2130,10 +2129,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>443515</v>
+        <v>443538</v>
       </c>
       <c r="R16" t="n">
-        <v>6767361</v>
+        <v>6767298</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2174,6 +2173,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2192,50 +2192,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127723016</v>
+        <v>127723068</v>
       </c>
       <c r="B17" t="n">
-        <v>8450</v>
+        <v>92693</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>1968</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>443673</v>
+        <v>443537</v>
       </c>
       <c r="R17" t="n">
-        <v>6767268</v>
+        <v>6767220</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2270,12 +2265,18 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Med grov gran i bäckmiljö</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2297,7 +2298,7 @@
         <v>127729140</v>
       </c>
       <c r="B18" t="n">
-        <v>92650</v>
+        <v>92661</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2413,45 +2414,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127723068</v>
+        <v>127723016</v>
       </c>
       <c r="B19" t="n">
-        <v>92682</v>
+        <v>8450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1968</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>443537</v>
+        <v>443673</v>
       </c>
       <c r="R19" t="n">
-        <v>6767220</v>
+        <v>6767268</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2486,18 +2492,12 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Med grov gran i bäckmiljö</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2621,7 +2621,7 @@
         <v>127723306</v>
       </c>
       <c r="B21" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>127723401</v>
       </c>
       <c r="B25" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>127722824</v>
       </c>
       <c r="B28" t="n">
-        <v>79650</v>
+        <v>79661</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3521,10 +3521,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127722980</v>
+        <v>127729074</v>
       </c>
       <c r="B30" t="n">
-        <v>8450</v>
+        <v>92673</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3532,39 +3532,45 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>4366</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>443513</v>
+        <v>443523</v>
       </c>
       <c r="R30" t="n">
-        <v>6767360</v>
+        <v>6767226</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3594,39 +3600,50 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127729074</v>
+        <v>127722980</v>
       </c>
       <c r="B31" t="n">
-        <v>92662</v>
+        <v>8450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3634,45 +3651,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4366</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>443523</v>
+        <v>443513</v>
       </c>
       <c r="R31" t="n">
-        <v>6767226</v>
+        <v>6767360</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3702,40 +3713,29 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>17:22</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>17:22</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3745,7 +3745,7 @@
         <v>127729095</v>
       </c>
       <c r="B32" t="n">
-        <v>92682</v>
+        <v>92693</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>127722869</v>
       </c>
       <c r="B34" t="n">
-        <v>57833</v>
+        <v>57844</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 35485-2025 artfynd.xlsx
+++ b/artfynd/A 35485-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>60771885</v>
+        <v>127723575</v>
       </c>
       <c r="B2" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Oxeråsen S om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>443486.3899851252</v>
+        <v>443456</v>
       </c>
       <c r="R2" t="n">
-        <v>6767363.45114645</v>
+        <v>6767338</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-07-28</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-07-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,72 +760,57 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bo karlstens, Bengt Oldhammer, Thorleif Joelson, martin eriksson, David Tverling</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2016 Dalarna</t>
-        </is>
-      </c>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127613328</v>
+        <v>127723576</v>
       </c>
       <c r="B3" t="n">
-        <v>92654</v>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4366</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Oxeråsen S om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>443545</v>
+        <v>443532</v>
       </c>
       <c r="R3" t="n">
-        <v>6767246</v>
+        <v>6767258</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,29 +851,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127723307</v>
+        <v>127723054</v>
       </c>
       <c r="B4" t="n">
-        <v>79043</v>
+        <v>81312</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -916,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -940,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>443521</v>
+        <v>443535</v>
       </c>
       <c r="R4" t="n">
-        <v>6767377</v>
+        <v>6767296</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127723609</v>
+        <v>127723068</v>
       </c>
       <c r="B5" t="n">
-        <v>78021</v>
+        <v>93231</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1013,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6487</v>
+        <v>1968</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1037,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>443546</v>
+        <v>443537</v>
       </c>
       <c r="R5" t="n">
-        <v>6767277</v>
+        <v>6767220</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1077,7 +1041,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På naturlig högstubbe med fyra brandljud</t>
+          <t>Med grov gran i bäckmiljö</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1086,6 +1050,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1104,10 +1069,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127723576</v>
+        <v>127729095</v>
       </c>
       <c r="B6" t="n">
-        <v>78710</v>
+        <v>93231</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1115,34 +1080,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>1968</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>443532</v>
+        <v>443537</v>
       </c>
       <c r="R6" t="n">
-        <v>6767258</v>
+        <v>6767222</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1172,9 +1137,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>17:18</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1189,22 +1164,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127723402</v>
+        <v>60771906</v>
       </c>
       <c r="B7" t="n">
-        <v>79043</v>
+        <v>93191</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1212,34 +1187,44 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S om, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>443667</v>
+        <v>443548</v>
       </c>
       <c r="R7" t="n">
-        <v>6767260</v>
+        <v>6767202</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,12 +1251,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2016-07-28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2016-07-28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1280,28 +1265,33 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Bo karlstens, Bengt Oldhammer, Thorleif Joelson, martin eriksson, David Tverling</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2016 Dalarna</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127722866</v>
+        <v>127723556</v>
       </c>
       <c r="B8" t="n">
-        <v>57684</v>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1309,39 +1299,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>443824</v>
+        <v>443515</v>
       </c>
       <c r="R8" t="n">
-        <v>6767217</v>
+        <v>6767361</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1400,50 +1385,56 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127723015</v>
+        <v>127729140</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>443662</v>
+        <v>443528</v>
       </c>
       <c r="R9" t="n">
-        <v>6767258</v>
+        <v>6767247</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1473,79 +1464,96 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127723012</v>
+        <v>127613328</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>93209</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>4366</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S om, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>443607</v>
+        <v>443545</v>
       </c>
       <c r="R10" t="n">
-        <v>6767249</v>
+        <v>6767246</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1572,12 +1580,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1586,28 +1594,29 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127723309</v>
+        <v>127729074</v>
       </c>
       <c r="B11" t="n">
-        <v>79043</v>
+        <v>93209</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1615,34 +1624,45 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
         <v>443523</v>
       </c>
       <c r="R11" t="n">
-        <v>6767394</v>
+        <v>6767226</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1672,43 +1692,54 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127723308</v>
+        <v>127723305</v>
       </c>
       <c r="B12" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1736,10 +1767,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>443530</v>
+        <v>443445</v>
       </c>
       <c r="R12" t="n">
-        <v>6767386</v>
+        <v>6767338</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1798,32 +1829,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127723556</v>
+        <v>127723306</v>
       </c>
       <c r="B13" t="n">
-        <v>92661</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1833,10 +1864,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>443515</v>
+        <v>443504</v>
       </c>
       <c r="R13" t="n">
-        <v>6767361</v>
+        <v>6767355</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1895,50 +1926,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127723014</v>
+        <v>127723307</v>
       </c>
       <c r="B14" t="n">
-        <v>8450</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>443651</v>
+        <v>443521</v>
       </c>
       <c r="R14" t="n">
-        <v>6767277</v>
+        <v>6767377</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1997,32 +2023,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127723054</v>
+        <v>127723308</v>
       </c>
       <c r="B15" t="n">
-        <v>81018</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2032,10 +2058,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>443535</v>
+        <v>443530</v>
       </c>
       <c r="R15" t="n">
-        <v>6767296</v>
+        <v>6767386</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2094,32 +2120,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127723059</v>
+        <v>127723309</v>
       </c>
       <c r="B16" t="n">
-        <v>78801</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2129,10 +2155,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>443538</v>
+        <v>443523</v>
       </c>
       <c r="R16" t="n">
-        <v>6767298</v>
+        <v>6767394</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2173,7 +2199,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2192,32 +2217,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127723068</v>
+        <v>127723401</v>
       </c>
       <c r="B17" t="n">
-        <v>92693</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1968</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2227,10 +2252,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>443537</v>
+        <v>443653</v>
       </c>
       <c r="R17" t="n">
-        <v>6767220</v>
+        <v>6767260</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2265,18 +2290,12 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Med grov gran i bäckmiljö</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2295,56 +2314,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127729140</v>
+        <v>127723402</v>
       </c>
       <c r="B18" t="n">
-        <v>92661</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>443528</v>
+        <v>443667</v>
       </c>
       <c r="R18" t="n">
-        <v>6767247</v>
+        <v>6767260</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2374,90 +2382,74 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>17:24</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>17:24</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127723016</v>
+        <v>127729099</v>
       </c>
       <c r="B19" t="n">
-        <v>8450</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>443673</v>
+        <v>443626</v>
       </c>
       <c r="R19" t="n">
-        <v>6767268</v>
+        <v>6767208</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2487,79 +2479,85 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127723017</v>
+        <v>127723058</v>
       </c>
       <c r="B20" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>443679</v>
+        <v>443456</v>
       </c>
       <c r="R20" t="n">
-        <v>6767256</v>
+        <v>6767338</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2600,6 +2598,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2618,10 +2617,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127723306</v>
+        <v>127723059</v>
       </c>
       <c r="B21" t="n">
-        <v>79043</v>
+        <v>79084</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2629,21 +2628,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2652,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>443504</v>
+        <v>443538</v>
       </c>
       <c r="R21" t="n">
-        <v>6767355</v>
+        <v>6767298</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2697,6 +2696,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2715,50 +2715,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127722979</v>
+        <v>73919759</v>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>79946</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Dalarna, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>443487</v>
+        <v>443510</v>
       </c>
       <c r="R22" t="n">
-        <v>6767358</v>
+        <v>6767418</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2785,12 +2780,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2018-09-01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2018-09-01</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2805,62 +2800,57 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Ville Pokela</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Ville Pokela</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127723019</v>
+        <v>127722824</v>
       </c>
       <c r="B23" t="n">
-        <v>8450</v>
+        <v>79946</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>443716</v>
+        <v>443688</v>
       </c>
       <c r="R23" t="n">
-        <v>6767260</v>
+        <v>6767261</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,50 +2909,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127722984</v>
+        <v>127723609</v>
       </c>
       <c r="B24" t="n">
-        <v>8450</v>
+        <v>78334</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6487</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>443515</v>
+        <v>443546</v>
       </c>
       <c r="R24" t="n">
-        <v>6767222</v>
+        <v>6767277</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2995,6 +2980,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På naturlig högstubbe med fyra brandljud</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3021,10 +3011,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127723401</v>
+        <v>127722866</v>
       </c>
       <c r="B25" t="n">
-        <v>79043</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3032,34 +3022,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>443653</v>
+        <v>443824</v>
       </c>
       <c r="R25" t="n">
-        <v>6767260</v>
+        <v>6767217</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3118,38 +3113,38 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127722982</v>
+        <v>127722869</v>
       </c>
       <c r="B26" t="n">
-        <v>8450</v>
+        <v>58114</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3158,10 +3153,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>443563</v>
+        <v>443535</v>
       </c>
       <c r="R26" t="n">
-        <v>6767324</v>
+        <v>6767220</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3220,10 +3215,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127723018</v>
+        <v>60771885</v>
       </c>
       <c r="B27" t="n">
-        <v>8450</v>
+        <v>8455</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3249,21 +3244,21 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S om, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>443697</v>
+        <v>443486</v>
       </c>
       <c r="R27" t="n">
-        <v>6767275</v>
+        <v>6767363</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3290,12 +3285,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2016-07-28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2016-07-28</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3310,57 +3305,66 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Bo karlstens, Bengt Oldhammer, Thorleif Joelson, martin eriksson, David Tverling</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2016 Dalarna</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127722824</v>
+        <v>127722934</v>
       </c>
       <c r="B28" t="n">
-        <v>79661</v>
+        <v>8455</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>443688</v>
+        <v>443450</v>
       </c>
       <c r="R28" t="n">
-        <v>6767261</v>
+        <v>6767433</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3419,10 +3423,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127723013</v>
+        <v>127722978</v>
       </c>
       <c r="B29" t="n">
-        <v>8450</v>
+        <v>8455</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3459,10 +3463,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>443647</v>
+        <v>443461</v>
       </c>
       <c r="R29" t="n">
-        <v>6767284</v>
+        <v>6767355</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3521,10 +3525,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127729074</v>
+        <v>127722979</v>
       </c>
       <c r="B30" t="n">
-        <v>92673</v>
+        <v>8455</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3532,45 +3536,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4366</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>443523</v>
+        <v>443487</v>
       </c>
       <c r="R30" t="n">
-        <v>6767226</v>
+        <v>6767358</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3600,40 +3598,29 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>17:22</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>17:22</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3643,7 +3630,7 @@
         <v>127722980</v>
       </c>
       <c r="B31" t="n">
-        <v>8450</v>
+        <v>8455</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3742,45 +3729,50 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127729095</v>
+        <v>127722981</v>
       </c>
       <c r="B32" t="n">
-        <v>92693</v>
+        <v>8455</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1968</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>443537</v>
+        <v>443608</v>
       </c>
       <c r="R32" t="n">
-        <v>6767222</v>
+        <v>6767339</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3810,19 +3802,9 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>17:18</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>17:18</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3837,22 +3819,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127722983</v>
+        <v>127722982</v>
       </c>
       <c r="B33" t="n">
-        <v>8450</v>
+        <v>8455</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3889,10 +3871,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>443544</v>
+        <v>443563</v>
       </c>
       <c r="R33" t="n">
-        <v>6767299</v>
+        <v>6767324</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3951,38 +3933,38 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127722869</v>
+        <v>127722983</v>
       </c>
       <c r="B34" t="n">
-        <v>57844</v>
+        <v>8455</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -3991,10 +3973,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>443535</v>
+        <v>443544</v>
       </c>
       <c r="R34" t="n">
-        <v>6767220</v>
+        <v>6767299</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4050,6 +4032,1123 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>127722984</v>
+      </c>
+      <c r="B35" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>443515</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6767222</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>127723011</v>
+      </c>
+      <c r="B36" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>443590</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6767237</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>127723012</v>
+      </c>
+      <c r="B37" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>443607</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6767249</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>127723013</v>
+      </c>
+      <c r="B38" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>443647</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6767284</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>127723014</v>
+      </c>
+      <c r="B39" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>443651</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6767277</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>127723015</v>
+      </c>
+      <c r="B40" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>443662</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6767258</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>127723016</v>
+      </c>
+      <c r="B41" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>443673</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6767268</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>127723017</v>
+      </c>
+      <c r="B42" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>443679</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6767256</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>127723018</v>
+      </c>
+      <c r="B43" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>443697</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6767275</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>127723019</v>
+      </c>
+      <c r="B44" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>443716</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6767260</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>127723043</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>443456</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6767337</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35485-2025 artfynd.xlsx
+++ b/artfynd/A 35485-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AZ45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723575</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723576</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723054</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1066,6 +1086,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723068</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1173,6 +1198,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729095</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1285,6 +1315,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2016 Dalarna</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60771906</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1382,6 +1417,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723556</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1501,6 +1541,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729140</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1610,6 +1655,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127613328</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1729,6 +1779,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729074</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1826,6 +1881,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723305</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1923,6 +1983,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723306</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2020,6 +2085,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723307</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2117,6 +2187,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723308</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2214,6 +2289,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723309</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2311,6 +2391,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723401</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2408,6 +2493,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723402</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2516,6 +2606,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729099</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2614,6 +2709,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723058</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2712,6 +2812,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723059</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2809,6 +2914,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73919759</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2906,6 +3016,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722824</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3008,6 +3123,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723609</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3110,6 +3230,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722866</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3212,6 +3337,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722869</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3318,6 +3448,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2016 Dalarna</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60771885</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3420,6 +3555,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722934</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3522,6 +3662,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722978</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3624,6 +3769,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722979</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3726,6 +3876,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722980</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3828,6 +3983,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722981</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3930,6 +4090,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722982</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4032,6 +4197,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722983</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4134,6 +4304,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722984</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4236,6 +4411,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723011</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4338,6 +4518,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723012</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4440,6 +4625,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723013</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4542,6 +4732,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723014</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4644,6 +4839,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723015</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4746,6 +4946,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723016</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4848,6 +5053,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723017</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4950,6 +5160,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723018</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5052,6 +5267,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723019</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5149,8 +5369,59 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723043</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>